--- a/scripts/i18n.xlsx
+++ b/scripts/i18n.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="908">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="912">
   <si>
     <t xml:space="preserve">페이지는 [피그마] PFPlay GUI 설계서 합본의 페이지 이름입니다. </t>
   </si>
@@ -2033,6 +2033,18 @@
   </si>
   <si>
     <t>Emergency Notice</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>system.announcement.notice.label</t>
+  </si>
+  <si>
+    <t>전체 공지</t>
+  </si>
+  <si>
+    <t>Notice</t>
   </si>
   <si>
     <t>bug_report.btn.open</t>
@@ -3136,7 +3148,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:M310"/>
+  <dimension ref="A1:M311"/>
   <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="12.6640625" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20.1640625" customWidth="1"/>
@@ -7815,950 +7827,967 @@
         <v>663</v>
       </c>
     </row>
-    <row r="225" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>664</v>
+      </c>
+      <c r="B225" t="s">
+        <v>664</v>
+      </c>
       <c r="C225" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D225" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="E225" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="226" spans="3:5" x14ac:dyDescent="0.25">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C226" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="D226" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E226" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C227" t="s">
+        <v>671</v>
+      </c>
+      <c r="D227" t="s">
+        <v>672</v>
+      </c>
+      <c r="E227" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C228" t="s">
+        <v>674</v>
+      </c>
+      <c r="D228" t="s">
+        <v>24</v>
+      </c>
+      <c r="E228" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C229" t="s">
+        <v>675</v>
+      </c>
+      <c r="D229" t="s">
         <v>669</v>
       </c>
-    </row>
-    <row r="227" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C227" t="s">
+      <c r="E229" t="s">
         <v>670</v>
       </c>
-      <c r="D227" t="s">
-        <v>24</v>
-      </c>
-      <c r="E227" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="228" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C228" t="s">
-        <v>671</v>
-      </c>
-      <c r="D228" t="s">
-        <v>665</v>
-      </c>
-      <c r="E228" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="229" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C229" t="s">
-        <v>672</v>
-      </c>
-      <c r="D229" t="s">
-        <v>673</v>
-      </c>
-      <c r="E229" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="230" spans="3:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C230" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D230" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E230" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="231" spans="3:5" x14ac:dyDescent="0.25">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C231" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="D231" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="E231" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="232" spans="3:5" x14ac:dyDescent="0.25">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C232" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D232" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E232" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="233" spans="3:5" x14ac:dyDescent="0.25">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C233" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D233" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="E233" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="234" spans="3:5" x14ac:dyDescent="0.25">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C234" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D234" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E234" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="235" spans="3:5" x14ac:dyDescent="0.25">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C235" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="D235" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="E235" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="236" spans="3:5" x14ac:dyDescent="0.25">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C236" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D236" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E236" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="237" spans="3:5" x14ac:dyDescent="0.25">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C237" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D237" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E237" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="238" spans="3:5" x14ac:dyDescent="0.25">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C238" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="D238" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="E238" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="239" spans="3:5" x14ac:dyDescent="0.25">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C239" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="D239" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="E239" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="240" spans="3:5" x14ac:dyDescent="0.25">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C240" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D240" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="E240" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="241" spans="3:5" x14ac:dyDescent="0.25">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C241" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D241" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="E241" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="242" spans="3:5" x14ac:dyDescent="0.25">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C242" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D242" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="E242" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="243" spans="3:5" x14ac:dyDescent="0.25">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C243" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="D243" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="E243" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="244" spans="3:5" x14ac:dyDescent="0.25">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C244" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D244" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="E244" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="245" spans="3:5" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C245" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="D245" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="E245" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="246" spans="3:5" x14ac:dyDescent="0.25">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C246" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="D246" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="E246" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="247" spans="3:5" x14ac:dyDescent="0.25">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C247" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="D247" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="E247" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="248" spans="3:5" x14ac:dyDescent="0.25">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C248" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="D248" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="E248" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="249" spans="3:5" x14ac:dyDescent="0.25">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C249" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="D249" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="E249" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="250" spans="3:5" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C250" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="D250" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="E250" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="251" spans="3:5" x14ac:dyDescent="0.25">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C251" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="D251" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="E251" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="252" spans="3:5" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C252" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D252" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="E252" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="253" spans="3:5" x14ac:dyDescent="0.25">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C253" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="D253" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="E253" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="254" spans="3:5" x14ac:dyDescent="0.25">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C254" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D254" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="E254" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="255" spans="3:5" x14ac:dyDescent="0.25">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C255" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="D255" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="E255" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="256" spans="3:5" x14ac:dyDescent="0.25">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C256" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="D256" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="E256" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="257" spans="3:5" x14ac:dyDescent="0.25">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C257" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="D257" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="E257" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="258" spans="3:5" x14ac:dyDescent="0.25">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C258" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="D258" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="E258" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="259" spans="3:5" x14ac:dyDescent="0.25">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C259" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="D259" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="E259" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="260" spans="3:5" x14ac:dyDescent="0.25">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C260" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="D260" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="E260" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="261" spans="3:5" x14ac:dyDescent="0.25">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C261" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="D261" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="E261" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="262" spans="3:5" x14ac:dyDescent="0.25">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C262" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="D262" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="E262" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="263" spans="3:5" x14ac:dyDescent="0.25">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C263" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="D263" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="E263" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="264" spans="3:5" x14ac:dyDescent="0.25">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C264" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D264" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="E264" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="265" spans="3:5" x14ac:dyDescent="0.25">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C265" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="D265" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="E265" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="266" spans="3:5" x14ac:dyDescent="0.25">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C266" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="D266" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="E266" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="267" spans="3:5" x14ac:dyDescent="0.25">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C267" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="D267" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="E267" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="268" spans="3:5" x14ac:dyDescent="0.25">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C268" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="D268" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="E268" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C269" t="s">
+        <v>790</v>
+      </c>
+      <c r="D269" t="s">
+        <v>791</v>
+      </c>
+      <c r="E269" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="269" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C269" t="s">
-        <v>788</v>
-      </c>
-      <c r="D269" t="s">
-        <v>789</v>
-      </c>
-      <c r="E269" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="270" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C270" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="D270" t="s">
+        <v>793</v>
+      </c>
+      <c r="E270" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C271" t="s">
+        <v>795</v>
+      </c>
+      <c r="D271" t="s">
         <v>514</v>
       </c>
-      <c r="E270" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="271" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C271" t="s">
-        <v>793</v>
-      </c>
-      <c r="D271" t="s">
-        <v>794</v>
-      </c>
       <c r="E271" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="272" spans="3:5" x14ac:dyDescent="0.25">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C272" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="D272" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="E272" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="273" spans="3:5" x14ac:dyDescent="0.25">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C273" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D273" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="E273" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="274" spans="3:5" x14ac:dyDescent="0.25">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C274" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D274" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="E274" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="275" spans="3:5" x14ac:dyDescent="0.25">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C275" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D275" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="E275" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C276" t="s">
+        <v>809</v>
+      </c>
+      <c r="D276" t="s">
+        <v>810</v>
+      </c>
+      <c r="E276" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="276" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C276" t="s">
-        <v>807</v>
-      </c>
-      <c r="D276" t="s">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C277" t="s">
+        <v>811</v>
+      </c>
+      <c r="D277" t="s">
         <v>57</v>
       </c>
-      <c r="E276" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="277" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C277" t="s">
-        <v>809</v>
-      </c>
-      <c r="D277" t="s">
-        <v>810</v>
-      </c>
       <c r="E277" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="278" spans="3:5" x14ac:dyDescent="0.25">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C278" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="D278" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="E278" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="279" spans="3:5" x14ac:dyDescent="0.25">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C279" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="D279" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="E279" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="280" spans="3:5" x14ac:dyDescent="0.25">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C280" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="D280" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="E280" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="281" spans="3:5" x14ac:dyDescent="0.25">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C281" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="D281" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="E281" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="282" spans="3:5" x14ac:dyDescent="0.25">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C282" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="D282" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="E282" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="283" spans="3:5" x14ac:dyDescent="0.25">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C283" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="D283" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="E283" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="284" spans="3:5" x14ac:dyDescent="0.25">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C284" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="D284" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="E284" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="285" spans="3:5" x14ac:dyDescent="0.25">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C285" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="D285" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="E285" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="286" spans="3:5" x14ac:dyDescent="0.25">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C286" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="D286" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E286" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="287" spans="3:5" x14ac:dyDescent="0.25">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C287" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="D287" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="E287" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="288" spans="3:5" x14ac:dyDescent="0.25">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C288" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="D288" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="E288" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="289" spans="3:5" x14ac:dyDescent="0.25">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C289" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="D289" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="E289" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C290" t="s">
+        <v>849</v>
+      </c>
+      <c r="D290" t="s">
+        <v>850</v>
+      </c>
+      <c r="E290" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="290" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C290" t="s">
-        <v>847</v>
-      </c>
-      <c r="D290" t="s">
-        <v>848</v>
-      </c>
-      <c r="E290" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="291" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C291" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="D291" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="E291" t="s">
-        <v>852</v>
-      </c>
-    </row>
-    <row r="292" spans="3:5" x14ac:dyDescent="0.25">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C292" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="D292" t="s">
+        <v>855</v>
+      </c>
+      <c r="E292" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C293" t="s">
+        <v>857</v>
+      </c>
+      <c r="D293" t="s">
         <v>440</v>
       </c>
-      <c r="E292" t="s">
+      <c r="E293" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="293" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C293" t="s">
-        <v>854</v>
-      </c>
-      <c r="D293" t="s">
-        <v>855</v>
-      </c>
-      <c r="E293" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="294" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C294" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="D294" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="E294" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="295" spans="3:5" x14ac:dyDescent="0.25">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C295" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="D295" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="E295" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="296" spans="3:5" x14ac:dyDescent="0.25">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C296" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="D296" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="E296" t="s">
-        <v>865</v>
-      </c>
-    </row>
-    <row r="297" spans="3:5" x14ac:dyDescent="0.25">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C297" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="D297" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="E297" t="s">
-        <v>868</v>
-      </c>
-    </row>
-    <row r="298" spans="3:5" x14ac:dyDescent="0.25">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C298" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="D298" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="E298" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="299" spans="3:5" x14ac:dyDescent="0.25">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C299" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="D299" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="E299" t="s">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="300" spans="3:5" x14ac:dyDescent="0.25">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C300" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D300" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="E300" t="s">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="301" spans="3:5" x14ac:dyDescent="0.25">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C301" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="D301" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="E301" t="s">
-        <v>880</v>
-      </c>
-    </row>
-    <row r="302" spans="3:5" x14ac:dyDescent="0.25">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C302" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="D302" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="E302" t="s">
-        <v>883</v>
-      </c>
-    </row>
-    <row r="303" spans="3:5" x14ac:dyDescent="0.25">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C303" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="D303" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="E303" t="s">
-        <v>886</v>
-      </c>
-    </row>
-    <row r="304" spans="3:5" x14ac:dyDescent="0.25">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C304" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="D304" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="E304" t="s">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="305" spans="3:5" x14ac:dyDescent="0.25">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C305" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="D305" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="E305" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="306" spans="3:5" x14ac:dyDescent="0.25">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C306" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="D306" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="E306" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="307" spans="3:5" x14ac:dyDescent="0.25">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C307" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="D307" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="E307" t="s">
-        <v>898</v>
-      </c>
-    </row>
-    <row r="308" spans="3:5" x14ac:dyDescent="0.25">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C308" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="D308" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="E308" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="309" spans="3:5" x14ac:dyDescent="0.25">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C309" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="D309" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="E309" t="s">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="310" spans="3:5" x14ac:dyDescent="0.25">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C310" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="D310" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="E310" t="s">
-        <v>907</v>
+        <v>908</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C311" t="s">
+        <v>909</v>
+      </c>
+      <c r="D311" t="s">
+        <v>910</v>
+      </c>
+      <c r="E311" t="s">
+        <v>911</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/i18n.xlsx
+++ b/scripts/i18n.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="912">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="934">
   <si>
     <t xml:space="preserve">페이지는 [피그마] PFPlay GUI 설계서 합본의 페이지 이름입니다. </t>
   </si>
@@ -2781,6 +2781,72 @@
   </si>
   <si>
     <t>Open your browser menu and choose &lt;b&gt;Add to Home screen&lt;/b&gt; (or Install app).</t>
+  </si>
+  <si>
+    <t>partyroom.queue.empty_cta</t>
+  </si>
+  <si>
+    <t>지금 당장 &lt;b&gt;DJ 대기열&lt;/b&gt;에서 시작해 보세요!</t>
+  </si>
+  <si>
+    <t>Start playing from the &lt;b&gt;DJ queue&lt;/b&gt; now!</t>
+  </si>
+  <si>
+    <t>common.btn.back</t>
+  </si>
+  <si>
+    <t>뒤로</t>
+  </si>
+  <si>
+    <t>Back</t>
+  </si>
+  <si>
+    <t>common.btn.close</t>
+  </si>
+  <si>
+    <t>common.btn.view_profile</t>
+  </si>
+  <si>
+    <t>프로필 보기</t>
+  </si>
+  <si>
+    <t>View profile</t>
+  </si>
+  <si>
+    <t>chat.title.live</t>
+  </si>
+  <si>
+    <t>실시간 채팅</t>
+  </si>
+  <si>
+    <t>Live chat</t>
+  </si>
+  <si>
+    <t>playlist.btn.preview_song</t>
+  </si>
+  <si>
+    <t>미리듣기</t>
+  </si>
+  <si>
+    <t>Preview</t>
+  </si>
+  <si>
+    <t>dj.title.select_song</t>
+  </si>
+  <si>
+    <t>곡 선택</t>
+  </si>
+  <si>
+    <t>Select a song</t>
+  </si>
+  <si>
+    <t>partyroom.para.listening_count</t>
+  </si>
+  <si>
+    <t>{{count}}명 청취 중</t>
+  </si>
+  <si>
+    <t>{{count}} listening</t>
   </si>
 </sst>
 </file>
@@ -3148,7 +3214,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:M311"/>
+  <dimension ref="A1:M319"/>
   <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="12.6640625" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20.1640625" customWidth="1"/>
@@ -7844,7 +7910,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="226" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C226" t="s">
         <v>668</v>
       </c>
@@ -7855,7 +7921,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="227" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C227" t="s">
         <v>671</v>
       </c>
@@ -7866,7 +7932,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="228" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C228" t="s">
         <v>674</v>
       </c>
@@ -7877,7 +7943,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="229" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C229" t="s">
         <v>675</v>
       </c>
@@ -7888,7 +7954,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="230" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C230" t="s">
         <v>676</v>
       </c>
@@ -7899,7 +7965,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="231" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C231" t="s">
         <v>679</v>
       </c>
@@ -7910,7 +7976,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="232" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C232" t="s">
         <v>682</v>
       </c>
@@ -7921,7 +7987,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="233" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C233" t="s">
         <v>685</v>
       </c>
@@ -7932,7 +7998,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="234" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C234" t="s">
         <v>688</v>
       </c>
@@ -7943,7 +8009,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="235" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C235" t="s">
         <v>691</v>
       </c>
@@ -7954,7 +8020,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="236" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C236" t="s">
         <v>694</v>
       </c>
@@ -7965,7 +8031,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="237" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C237" t="s">
         <v>697</v>
       </c>
@@ -7976,7 +8042,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="238" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C238" t="s">
         <v>700</v>
       </c>
@@ -7987,7 +8053,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="239" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C239" t="s">
         <v>703</v>
       </c>
@@ -7998,7 +8064,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="240" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C240" t="s">
         <v>706</v>
       </c>
@@ -8009,7 +8075,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="241" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C241" t="s">
         <v>709</v>
       </c>
@@ -8020,7 +8086,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="242" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C242" t="s">
         <v>712</v>
       </c>
@@ -8031,7 +8097,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="243" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C243" t="s">
         <v>714</v>
       </c>
@@ -8042,7 +8108,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="244" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C244" t="s">
         <v>717</v>
       </c>
@@ -8053,7 +8119,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="245" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C245" t="s">
         <v>720</v>
       </c>
@@ -8064,7 +8130,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="246" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C246" t="s">
         <v>723</v>
       </c>
@@ -8075,7 +8141,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="247" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C247" t="s">
         <v>726</v>
       </c>
@@ -8086,7 +8152,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="248" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C248" t="s">
         <v>729</v>
       </c>
@@ -8097,7 +8163,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="249" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C249" t="s">
         <v>732</v>
       </c>
@@ -8108,7 +8174,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="250" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C250" t="s">
         <v>735</v>
       </c>
@@ -8119,7 +8185,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="251" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C251" t="s">
         <v>738</v>
       </c>
@@ -8130,7 +8196,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="252" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C252" t="s">
         <v>741</v>
       </c>
@@ -8141,7 +8207,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="253" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C253" t="s">
         <v>744</v>
       </c>
@@ -8152,7 +8218,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="254" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C254" t="s">
         <v>747</v>
       </c>
@@ -8163,7 +8229,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="255" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C255" t="s">
         <v>750</v>
       </c>
@@ -8174,7 +8240,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="256" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C256" t="s">
         <v>753</v>
       </c>
@@ -8185,7 +8251,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="257" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C257" t="s">
         <v>755</v>
       </c>
@@ -8196,7 +8262,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="258" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C258" t="s">
         <v>757</v>
       </c>
@@ -8207,7 +8273,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="259" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C259" t="s">
         <v>760</v>
       </c>
@@ -8218,7 +8284,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="260" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C260" t="s">
         <v>763</v>
       </c>
@@ -8229,7 +8295,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="261" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C261" t="s">
         <v>766</v>
       </c>
@@ -8240,7 +8306,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="262" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C262" t="s">
         <v>769</v>
       </c>
@@ -8251,7 +8317,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="263" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C263" t="s">
         <v>772</v>
       </c>
@@ -8262,7 +8328,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="264" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C264" t="s">
         <v>775</v>
       </c>
@@ -8273,7 +8339,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="265" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C265" t="s">
         <v>778</v>
       </c>
@@ -8284,7 +8350,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="266" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C266" t="s">
         <v>781</v>
       </c>
@@ -8295,7 +8361,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="267" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C267" t="s">
         <v>784</v>
       </c>
@@ -8306,7 +8372,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="268" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C268" t="s">
         <v>787</v>
       </c>
@@ -8317,7 +8383,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="269" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C269" t="s">
         <v>790</v>
       </c>
@@ -8328,7 +8394,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="270" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C270" t="s">
         <v>792</v>
       </c>
@@ -8339,7 +8405,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="271" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C271" t="s">
         <v>795</v>
       </c>
@@ -8350,7 +8416,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="272" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C272" t="s">
         <v>797</v>
       </c>
@@ -8361,7 +8427,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="273" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C273" t="s">
         <v>800</v>
       </c>
@@ -8372,7 +8438,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="274" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C274" t="s">
         <v>803</v>
       </c>
@@ -8383,7 +8449,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="275" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C275" t="s">
         <v>806</v>
       </c>
@@ -8394,7 +8460,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="276" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C276" t="s">
         <v>809</v>
       </c>
@@ -8405,7 +8471,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="277" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C277" t="s">
         <v>811</v>
       </c>
@@ -8416,7 +8482,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="278" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C278" t="s">
         <v>813</v>
       </c>
@@ -8427,7 +8493,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="279" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C279" t="s">
         <v>816</v>
       </c>
@@ -8438,7 +8504,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="280" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C280" t="s">
         <v>819</v>
       </c>
@@ -8449,7 +8515,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="281" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C281" t="s">
         <v>822</v>
       </c>
@@ -8460,7 +8526,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="282" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C282" t="s">
         <v>825</v>
       </c>
@@ -8471,7 +8537,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="283" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C283" t="s">
         <v>828</v>
       </c>
@@ -8482,7 +8548,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="284" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C284" t="s">
         <v>831</v>
       </c>
@@ -8493,7 +8559,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="285" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C285" t="s">
         <v>834</v>
       </c>
@@ -8504,7 +8570,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="286" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C286" t="s">
         <v>837</v>
       </c>
@@ -8515,7 +8581,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="287" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C287" t="s">
         <v>840</v>
       </c>
@@ -8526,7 +8592,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="288" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C288" t="s">
         <v>843</v>
       </c>
@@ -8537,7 +8603,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="289" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C289" t="s">
         <v>846</v>
       </c>
@@ -8548,7 +8614,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="290" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C290" t="s">
         <v>849</v>
       </c>
@@ -8559,7 +8625,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="291" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C291" t="s">
         <v>851</v>
       </c>
@@ -8570,7 +8636,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="292" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C292" t="s">
         <v>854</v>
       </c>
@@ -8581,7 +8647,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="293" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C293" t="s">
         <v>857</v>
       </c>
@@ -8592,7 +8658,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="294" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C294" t="s">
         <v>858</v>
       </c>
@@ -8603,7 +8669,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="295" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C295" t="s">
         <v>861</v>
       </c>
@@ -8614,7 +8680,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="296" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C296" t="s">
         <v>864</v>
       </c>
@@ -8625,7 +8691,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="297" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C297" t="s">
         <v>867</v>
       </c>
@@ -8636,7 +8702,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="298" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C298" t="s">
         <v>870</v>
       </c>
@@ -8647,7 +8713,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="299" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C299" t="s">
         <v>873</v>
       </c>
@@ -8658,7 +8724,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="300" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C300" t="s">
         <v>876</v>
       </c>
@@ -8669,7 +8735,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="301" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C301" t="s">
         <v>879</v>
       </c>
@@ -8680,7 +8746,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="302" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C302" t="s">
         <v>882</v>
       </c>
@@ -8691,7 +8757,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="303" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C303" t="s">
         <v>885</v>
       </c>
@@ -8702,7 +8768,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="304" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C304" t="s">
         <v>888</v>
       </c>
@@ -8713,7 +8779,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="305" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C305" t="s">
         <v>891</v>
       </c>
@@ -8724,7 +8790,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="306" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C306" t="s">
         <v>894</v>
       </c>
@@ -8735,7 +8801,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="307" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C307" t="s">
         <v>897</v>
       </c>
@@ -8746,7 +8812,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="308" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C308" t="s">
         <v>900</v>
       </c>
@@ -8757,7 +8823,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="309" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C309" t="s">
         <v>903</v>
       </c>
@@ -8768,7 +8834,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="310" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C310" t="s">
         <v>906</v>
       </c>
@@ -8779,7 +8845,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="311" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C311" t="s">
         <v>909</v>
       </c>
@@ -8788,6 +8854,94 @@
       </c>
       <c r="E311" t="s">
         <v>911</v>
+      </c>
+    </row>
+    <row r="312" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C312" t="s">
+        <v>912</v>
+      </c>
+      <c r="D312" t="s">
+        <v>913</v>
+      </c>
+      <c r="E312" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C313" t="s">
+        <v>915</v>
+      </c>
+      <c r="D313" t="s">
+        <v>916</v>
+      </c>
+      <c r="E313" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C314" t="s">
+        <v>918</v>
+      </c>
+      <c r="D314" t="s">
+        <v>660</v>
+      </c>
+      <c r="E314" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C315" t="s">
+        <v>919</v>
+      </c>
+      <c r="D315" t="s">
+        <v>920</v>
+      </c>
+      <c r="E315" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C316" t="s">
+        <v>922</v>
+      </c>
+      <c r="D316" t="s">
+        <v>923</v>
+      </c>
+      <c r="E316" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C317" t="s">
+        <v>925</v>
+      </c>
+      <c r="D317" t="s">
+        <v>926</v>
+      </c>
+      <c r="E317" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C318" t="s">
+        <v>928</v>
+      </c>
+      <c r="D318" t="s">
+        <v>929</v>
+      </c>
+      <c r="E318" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C319" t="s">
+        <v>931</v>
+      </c>
+      <c r="D319" t="s">
+        <v>932</v>
+      </c>
+      <c r="E319" t="s">
+        <v>933</v>
       </c>
     </row>
   </sheetData>
